--- a/Tagihan/2026/September/Camelia.xlsx
+++ b/Tagihan/2026/September/Camelia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\September\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDE9BC1B-16D5-47EA-86FC-7671AB028A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6667EED-DA6E-43B0-A741-C4E58A7E00CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Perbaikan" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>NO.</t>
   </si>
@@ -84,8 +84,17 @@
     <t>Pcs</t>
   </si>
   <si>
+    <t>Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merapikan Kabel CCTV Dan Reposisi Mesin  </t>
+  </si>
+  <si>
+    <t>Kepada Tuan/Nyonya  Camelia</t>
+  </si>
+  <si>
     <r>
-      <t>Tanjung,13</t>
+      <t>Tanjung,</t>
     </r>
     <r>
       <rPr>
@@ -95,26 +104,35 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> September 2026</t>
+      <t>22 September 2026</t>
     </r>
   </si>
   <si>
-    <t>Dukting</t>
-  </si>
-  <si>
-    <t>Konektor BNC</t>
-  </si>
-  <si>
-    <t>Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merapikan Kabel CCTV Dan Reposisi Mesin  </t>
-  </si>
-  <si>
-    <t>Biaya Perbaikan</t>
-  </si>
-  <si>
-    <t>Kepada Tuan/Nyonya  Camelia</t>
+    <t>Kamera Proview FC Audio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabel CCTV </t>
+  </si>
+  <si>
+    <t>Mtr</t>
+  </si>
+  <si>
+    <t>Harddisk 1TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *Tukar Tambah Harddisk 500GB Ke 1TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konektor </t>
+  </si>
+  <si>
+    <t>Biaya Instalasi</t>
+  </si>
+  <si>
+    <t>Duckting</t>
+  </si>
+  <si>
+    <t>Durados</t>
   </si>
 </sst>
 </file>
@@ -211,7 +229,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -361,7 +379,9 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -374,7 +394,9 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -385,11 +407,26 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
@@ -398,31 +435,9 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -503,10 +518,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -630,13 +645,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>59532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2403475</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>115571</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -971,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:H37"/>
+  <dimension ref="B5:H42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1038,7 +1053,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="45" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G13" s="45"/>
     </row>
@@ -1048,12 +1063,12 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="46" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G14" s="46"/>
     </row>
     <row r="15" spans="2:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>0</v>
       </c>
@@ -1074,212 +1089,313 @@
       </c>
     </row>
     <row r="17" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="2">
+      <c r="B17" s="23">
         <v>1</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="23">
+        <v>3</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="15">
+        <v>350000</v>
+      </c>
+      <c r="G17" s="15">
+        <f t="shared" ref="G17:G19" si="0">F17*D17</f>
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="2">
         <v>2</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16">
-        <f t="shared" ref="G17:G20" si="0">F17*D17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="23">
-        <v>2</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="23">
-        <v>2</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
-    </row>
-    <row r="19" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="2">
+        <v>143</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="16">
+        <v>5000</v>
+      </c>
+      <c r="G18" s="16">
+        <f t="shared" si="0"/>
+        <v>715000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2">
         <v>3</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D19" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="14">
-        <v>15000</v>
+        <v>16</v>
+      </c>
+      <c r="F19" s="16">
+        <v>800000</v>
       </c>
       <c r="G19" s="16">
         <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="2"/>
+      <c r="C20" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+    </row>
+    <row r="21" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="2">
+        <v>4</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="16">
+        <v>200000</v>
+      </c>
+      <c r="G21" s="16">
+        <f>F21*D21</f>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="2">
+        <v>5</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="23">
+        <v>3</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="14">
+        <v>15000</v>
+      </c>
+      <c r="G22" s="15">
+        <f>F22*D22</f>
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="2">
+        <v>6</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="23">
+        <v>3</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="14">
+        <v>35000</v>
+      </c>
+      <c r="G23" s="15">
+        <f t="shared" ref="G23:G25" si="1">F23*D23</f>
         <v>105000</v>
       </c>
     </row>
-    <row r="20" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="23">
-        <v>4</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2" t="s">
+    <row r="24" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="2">
+        <v>7</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="2">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="14">
+        <v>15000</v>
+      </c>
+      <c r="G24" s="16">
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="2">
+        <v>8</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="14">
-        <v>100000</v>
-      </c>
-      <c r="G20" s="16">
-        <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="23"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="15"/>
-    </row>
-    <row r="22" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="2"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="15"/>
-    </row>
-    <row r="23" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="23"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="15"/>
-    </row>
-    <row r="24" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="2"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="16"/>
-    </row>
-    <row r="25" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="2"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="16"/>
+      <c r="F25" s="14">
+        <v>150000</v>
+      </c>
+      <c r="G25" s="16">
+        <f t="shared" si="1"/>
+        <v>450000</v>
+      </c>
     </row>
     <row r="26" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
+      <c r="B26" s="23"/>
       <c r="C26" s="17"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="17"/>
+      <c r="E26" s="2"/>
       <c r="F26" s="14"/>
-      <c r="G26" s="16"/>
+      <c r="G26" s="15"/>
     </row>
     <row r="27" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
       <c r="C27" s="17"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="16"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="14"/>
       <c r="G27" s="15"/>
     </row>
-    <row r="28" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="40" t="s">
+    <row r="28" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="23"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="2"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="16"/>
+    </row>
+    <row r="30" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="2"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="16"/>
+    </row>
+    <row r="31" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="2"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="16"/>
+    </row>
+    <row r="32" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="15"/>
+    </row>
+    <row r="33" spans="2:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="18">
-        <f>SUM(G17:G27)</f>
-        <v>205000</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="8"/>
-    </row>
-    <row r="31" spans="2:7" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B31" s="43" t="s">
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="18">
+        <f>SUM(G17:G32)</f>
+        <v>3515000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="8"/>
+    </row>
+    <row r="36" spans="2:8" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B36" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="43"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="44" t="s">
+      <c r="C36" s="43"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="44"/>
-    </row>
-    <row r="35" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="38" t="s">
+      <c r="G36" s="44"/>
+    </row>
+    <row r="40" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="34"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="12"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="35" t="s">
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="12"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B42:G42"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B14:C14"/>
